--- a/exports/FR_Budget_Status.xlsx
+++ b/exports/FR_Budget_Status.xlsx
@@ -1078,11 +1078,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="5" t="inlineStr"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
           <t>OSW (CAPIN)</t>
@@ -2123,11 +2119,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="5" t="inlineStr"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
           <t>OSW (nirbhaya Fund)</t>

--- a/exports/FR_Budget_Status.xlsx
+++ b/exports/FR_Budget_Status.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 17." sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 27." sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 17.08.202" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 17.08." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 27.08.202" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 27.08." sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report - As On 17.08.2026</t>
+          <t>Open Line FR Report - As On 27.08.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -571,13 +571,13 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>77,164
+          <t>77,175
 Cr. 7.72</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>-83,739
+          <t>-83,728
 Cr. -8.37</t>
         </is>
       </c>
@@ -606,19 +606,19 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>8,452
-Cr. 0.85</t>
+          <t>10,761
+Cr. 1.08</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-23,775
-Cr. -2.38</t>
+          <t>-21,466
+Cr. -2.15</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>33.39</t>
         </is>
       </c>
     </row>
@@ -641,19 +641,19 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>55,924
-Cr. 5.59</t>
+          <t>57,023
+Cr. 5.70</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-64,394
-Cr. -6.44</t>
+          <t>-63,295
+Cr. -6.33</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>46.48</t>
+          <t>47.39</t>
         </is>
       </c>
     </row>
@@ -676,19 +676,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>327,869
-Cr. 32.79</t>
+          <t>337,625
+Cr. 33.76</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-179,551
-Cr. -17.96</t>
+          <t>-169,795
+Cr. -16.98</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>64.61</t>
+          <t>66.54</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3,070,343
-Cr. 307.03</t>
+          <t>3,110,796
+Cr. 311.08</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>107,548
-Cr. 10.75</t>
+          <t>148,001
+Cr. 14.80</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>103.63</t>
+          <t>105.00</t>
         </is>
       </c>
     </row>
@@ -746,19 +746,19 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>142,510
-Cr. 14.25</t>
+          <t>150,620
+Cr. 15.06</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>10,243
-Cr. 1.02</t>
+          <t>18,353
+Cr. 1.84</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>107.74</t>
+          <t>113.88</t>
         </is>
       </c>
     </row>
@@ -781,19 +781,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>120,694
-Cr. 12.07</t>
+          <t>120,775
+Cr. 12.08</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-402,149
+          <t>-402,068
 Cr. -40.21</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.10</t>
         </is>
       </c>
     </row>
@@ -816,19 +816,19 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>92,648
-Cr. 9.26</t>
+          <t>94,918
+Cr. 9.49</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-215,195
-Cr. -21.52</t>
+          <t>-212,925
+Cr. -21.29</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>30.10</t>
+          <t>30.83</t>
         </is>
       </c>
     </row>
@@ -956,19 +956,19 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>42,044
-Cr. 4.20</t>
+          <t>52,019
+Cr. 5.20</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-55,456
-Cr. -5.55</t>
+          <t>-45,481
+Cr. -4.55</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>43.12</t>
+          <t>53.35</t>
         </is>
       </c>
     </row>
@@ -991,19 +991,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>117,954
-Cr. 11.80</t>
+          <t>125,269
+Cr. 12.53</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-192,958
-Cr. -19.30</t>
+          <t>-185,643
+Cr. -18.56</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>40.29</t>
         </is>
       </c>
     </row>
@@ -1061,19 +1061,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>85,279
-Cr. 8.53</t>
+          <t>98,749
+Cr. 9.87</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>-230,454
-Cr. -23.05</t>
+          <t>-216,984
+Cr. -21.70</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>31.28</t>
         </is>
       </c>
     </row>
@@ -1158,19 +1158,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>4,155,709
-Cr. 415.57</t>
+          <t>4,250,558
+Cr. 425.06</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-1,451,992
-Cr. -145.20</t>
+          <t>-1,357,143
+Cr. -135.71</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>74.11</t>
+          <t>75.80</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise - As On 17.08.2026</t>
+          <t>Open Line FR Fund Wise - As On 27.08.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1275,24 +1275,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>354,585
-Cr. 35.46</t>
+          <t>380,485
+Cr. 38.05</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>663,768
-Cr. 66.38</t>
+          <t>637,868
+Cr. 63.79</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>37.36</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>65.18</t>
+          <t>62.64</t>
         </is>
       </c>
     </row>
@@ -1415,24 +1415,24 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>3,142,858
-Cr. 314.29</t>
+          <t>3,175,144
+Cr. 317.51</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>-25,343
-Cr. -2.53</t>
+          <t>-57,629
+Cr. -5.76</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>100.81</t>
+          <t>101.85</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.85</t>
         </is>
       </c>
     </row>
@@ -1485,24 +1485,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>631,485
-Cr. 63.15</t>
+          <t>668,148
+Cr. 66.81</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>669,524
-Cr. 66.95</t>
+          <t>632,861
+Cr. 63.29</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>48.54</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>51.46</t>
+          <t>48.64</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSU FR Report - As On 17.08.2026</t>
+          <t>GSU FR Report - As On 27.08.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2032,19 +2032,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>284,479
-Cr. 28.45</t>
+          <t>302,595
+Cr. 30.26</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-162,121
-Cr. -16.21</t>
+          <t>-144,005
+Cr. -14.40</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>67.76</t>
         </is>
       </c>
     </row>
@@ -2199,19 +2199,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>286,654
-Cr. 28.67</t>
+          <t>304,770
+Cr. 30.48</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-164,949
-Cr. -16.49</t>
+          <t>-146,833
+Cr. -14.68</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>67.49</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSU FR Fund Wise - As On 17.08.2026</t>
+          <t>GSU FR Fund Wise - As On 27.08.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2316,24 +2316,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>286,527
-Cr. 28.65</t>
+          <t>304,643
+Cr. 30.46</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>165,074
-Cr. 16.51</t>
+          <t>146,958
+Cr. 14.70</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>63.45</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>32.54</t>
         </is>
       </c>
     </row>

--- a/exports/FR_Budget_Status.xlsx
+++ b/exports/FR_Budget_Status.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 27." sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 27.08.202" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 27.08." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 05.09.202" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 05.09." sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report - As On 27.08.2026</t>
+          <t>Open Line FR Report - As On 05.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -571,19 +571,19 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>77,175
-Cr. 7.72</t>
+          <t>77,992
+Cr. 7.80</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>-83,728
-Cr. -8.37</t>
+          <t>-82,911
+Cr. -8.29</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>48.47</t>
         </is>
       </c>
     </row>
@@ -606,19 +606,19 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>10,761
-Cr. 1.08</t>
+          <t>11,801
+Cr. 1.18</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-21,466
-Cr. -2.15</t>
+          <t>-20,426
+Cr. -2.04</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>36.62</t>
         </is>
       </c>
     </row>
@@ -641,19 +641,19 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>57,023
-Cr. 5.70</t>
+          <t>57,289
+Cr. 5.73</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-63,295
-Cr. -6.33</t>
+          <t>-63,029
+Cr. -6.30</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>47.39</t>
+          <t>47.61</t>
         </is>
       </c>
     </row>
@@ -676,19 +676,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>337,625
-Cr. 33.76</t>
+          <t>363,937
+Cr. 36.39</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-169,795
-Cr. -16.98</t>
+          <t>-143,483
+Cr. -14.35</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>66.54</t>
+          <t>71.72</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3,110,796
-Cr. 311.08</t>
+          <t>3,692,699
+Cr. 369.27</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>148,001
-Cr. 14.80</t>
+          <t>729,904
+Cr. 72.99</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>105.00</t>
+          <t>124.64</t>
         </is>
       </c>
     </row>
@@ -746,19 +746,19 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>150,620
-Cr. 15.06</t>
+          <t>151,197
+Cr. 15.12</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>18,353
-Cr. 1.84</t>
+          <t>18,930
+Cr. 1.89</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>113.88</t>
+          <t>114.31</t>
         </is>
       </c>
     </row>
@@ -781,19 +781,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>120,775
-Cr. 12.08</t>
+          <t>123,038
+Cr. 12.30</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-402,068
-Cr. -40.21</t>
+          <t>-399,805
+Cr. -39.98</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>23.10</t>
+          <t>23.53</t>
         </is>
       </c>
     </row>
@@ -816,19 +816,19 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>94,918
+          <t>94,924
 Cr. 9.49</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-212,925
+          <t>-212,919
 Cr. -21.29</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>30.84</t>
         </is>
       </c>
     </row>
@@ -886,19 +886,19 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>10,501
-Cr. 1.05</t>
+          <t>24,273
+Cr. 2.43</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-2,693
-Cr. -0.27</t>
+          <t>11,079
+Cr. 1.11</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>79.59</t>
+          <t>183.97</t>
         </is>
       </c>
     </row>
@@ -921,19 +921,19 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>4,327
-Cr. 0.43</t>
+          <t>5,129
+Cr. 0.51</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-49,375
-Cr. -4.94</t>
+          <t>-48,573
+Cr. -4.86</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>9.55</t>
         </is>
       </c>
     </row>
@@ -956,19 +956,19 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>52,019
-Cr. 5.20</t>
+          <t>59,852
+Cr. 5.99</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-45,481
-Cr. -4.55</t>
+          <t>-37,648
+Cr. -3.76</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>53.35</t>
+          <t>61.39</t>
         </is>
       </c>
     </row>
@@ -991,19 +991,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>125,269
-Cr. 12.53</t>
+          <t>131,048
+Cr. 13.10</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-185,643
-Cr. -18.56</t>
+          <t>-179,864
+Cr. -17.99</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>40.29</t>
+          <t>42.15</t>
         </is>
       </c>
     </row>
@@ -1061,19 +1061,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>98,749
-Cr. 9.87</t>
+          <t>103,375
+Cr. 10.34</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>-216,984
-Cr. -21.70</t>
+          <t>-212,358
+Cr. -21.24</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>32.74</t>
         </is>
       </c>
     </row>
@@ -1158,19 +1158,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>4,250,558
-Cr. 425.06</t>
+          <t>4,896,554
+Cr. 489.66</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-1,357,143
-Cr. -135.71</t>
+          <t>-711,147
+Cr. -71.11</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>75.80</t>
+          <t>87.32</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise - As On 27.08.2026</t>
+          <t>Open Line FR Fund Wise - As On 05.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1275,24 +1275,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>380,485
-Cr. 38.05</t>
+          <t>408,842
+Cr. 40.88</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>637,868
-Cr. 63.79</t>
+          <t>609,511
+Cr. 60.95</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>37.36</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>62.64</t>
+          <t>59.85</t>
         </is>
       </c>
     </row>
@@ -1345,24 +1345,24 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>11,290
-Cr. 1.13</t>
+          <t>18,459
+Cr. 1.85</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>119,302
-Cr. 11.93</t>
+          <t>112,133
+Cr. 11.21</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>14.13</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>91.35</t>
+          <t>85.87</t>
         </is>
       </c>
     </row>
@@ -1415,24 +1415,24 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>3,175,144
-Cr. 317.51</t>
+          <t>3,746,106
+Cr. 374.61</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>-57,629
-Cr. -5.76</t>
+          <t>-628,591
+Cr. -62.86</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>101.85</t>
+          <t>120.16</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-20.16</t>
         </is>
       </c>
     </row>
@@ -1485,24 +1485,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>668,148
-Cr. 66.81</t>
+          <t>707,656
+Cr. 70.77</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>632,861
-Cr. 63.29</t>
+          <t>593,353
+Cr. 59.34</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>54.39</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>45.61</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSU FR Report - As On 27.08.2026</t>
+          <t>GSU FR Report - As On 05.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2032,19 +2032,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>302,595
-Cr. 30.26</t>
+          <t>317,088
+Cr. 31.71</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-144,005
-Cr. -14.40</t>
+          <t>-129,512
+Cr. -12.95</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>71.00</t>
         </is>
       </c>
     </row>
@@ -2199,19 +2199,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>304,770
-Cr. 30.48</t>
+          <t>319,263
+Cr. 31.93</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-146,833
-Cr. -14.68</t>
+          <t>-132,340
+Cr. -13.23</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>67.49</t>
+          <t>70.70</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSU FR Fund Wise - As On 27.08.2026</t>
+          <t>GSU FR Fund Wise - As On 05.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2316,24 +2316,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>304,643
-Cr. 30.46</t>
+          <t>319,136
+Cr. 31.91</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>146,958
-Cr. 14.70</t>
+          <t>132,465
+Cr. 13.25</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>32.54</t>
+          <t>29.33</t>
         </is>
       </c>
     </row>
